--- a/artfynd/A 17679-2026 artfynd.xlsx
+++ b/artfynd/A 17679-2026 artfynd.xlsx
@@ -822,7 +822,7 @@
         <v>132410216</v>
       </c>
       <c r="B3" t="n">
-        <v>58320</v>
+        <v>58322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17679-2026 artfynd.xlsx
+++ b/artfynd/A 17679-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -822,7 +822,7 @@
         <v>132410216</v>
       </c>
       <c r="B3" t="n">
-        <v>58322</v>
+        <v>58323</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -939,6 +939,120 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132659867</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56812</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Wängelistorpet, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>652369</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6650236</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2019-07-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2019-07-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17679-2026 artfynd.xlsx
+++ b/artfynd/A 17679-2026 artfynd.xlsx
@@ -822,7 +822,7 @@
         <v>132410216</v>
       </c>
       <c r="B3" t="n">
-        <v>58323</v>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>132659867</v>
       </c>
       <c r="B4" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 17679-2026 artfynd.xlsx
+++ b/artfynd/A 17679-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1054,6 +1054,122 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132850906</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58637</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Roparhällarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>652397</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6650215</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Vilhelm Amcoff</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Vilhelm Amcoff</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17679-2026 artfynd.xlsx
+++ b/artfynd/A 17679-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -822,7 +822,7 @@
         <v>132410216</v>
       </c>
       <c r="B3" t="n">
-        <v>58327</v>
+        <v>58328</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1170,6 +1170,1252 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132893090</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58637</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Adolfsbergsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>652486</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6650197</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132893072</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57547</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102963</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skrattmås</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chroicocephalus ridibundus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Adolfsbergsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>652486</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6650197</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132893083</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58677</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Adolfsbergsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>652486</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6650197</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132889683</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58637</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Adolfsbergsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>652469</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6650249</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132889677</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57547</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102963</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skrattmås</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Chroicocephalus ridibundus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Adolfsbergsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>652469</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6650249</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132889696</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58328</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Adolfsbergsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>652469</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6650249</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132889698</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58498</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Adolfsbergsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>652469</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6650249</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132893086</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58113</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Adolfsbergsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>652486</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6650197</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132893075</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58086</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Adolfsbergsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>652486</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6650197</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132889679</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57248</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100038</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Skogsduva</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Columba oenas</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Adolfsbergsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>652469</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6650249</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132889680</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58389</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Adolfsbergsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>652469</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6650249</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17679-2026 artfynd.xlsx
+++ b/artfynd/A 17679-2026 artfynd.xlsx
@@ -1737,10 +1737,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132889696</v>
+        <v>132889698</v>
       </c>
       <c r="B11" t="n">
-        <v>58328</v>
+        <v>58498</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,16 +1748,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1853,10 +1853,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132889698</v>
+        <v>132889696</v>
       </c>
       <c r="B12" t="n">
-        <v>58498</v>
+        <v>58328</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,16 +1864,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">

--- a/artfynd/A 17679-2026 artfynd.xlsx
+++ b/artfynd/A 17679-2026 artfynd.xlsx
@@ -1737,10 +1737,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132889698</v>
+        <v>132889696</v>
       </c>
       <c r="B11" t="n">
-        <v>58498</v>
+        <v>58328</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,16 +1748,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1853,10 +1853,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132889696</v>
+        <v>132889698</v>
       </c>
       <c r="B12" t="n">
-        <v>58328</v>
+        <v>58498</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,16 +1864,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">

--- a/artfynd/A 17679-2026 artfynd.xlsx
+++ b/artfynd/A 17679-2026 artfynd.xlsx
@@ -1733,10 +1733,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132889698</v>
+        <v>132889696</v>
       </c>
       <c r="B11" t="n">
-        <v>58502</v>
+        <v>58332</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1744,16 +1744,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1849,10 +1849,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132889696</v>
+        <v>132889698</v>
       </c>
       <c r="B12" t="n">
-        <v>58332</v>
+        <v>58502</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,16 +1860,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">

--- a/artfynd/A 17679-2026 artfynd.xlsx
+++ b/artfynd/A 17679-2026 artfynd.xlsx
@@ -1733,10 +1733,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132889696</v>
+        <v>132889698</v>
       </c>
       <c r="B11" t="n">
-        <v>58332</v>
+        <v>58502</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1744,16 +1744,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1849,10 +1849,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132889698</v>
+        <v>132889696</v>
       </c>
       <c r="B12" t="n">
-        <v>58502</v>
+        <v>58332</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,16 +1860,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">

--- a/artfynd/A 17679-2026 artfynd.xlsx
+++ b/artfynd/A 17679-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>57751934</v>
+        <v>132892100</v>
       </c>
       <c r="B2" t="n">
-        <v>89776</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57896</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,43 +686,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6040162</v>
+        <v>100001</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Adolfsbergsskogen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>652460.5916070903</v>
+        <v>652502</v>
       </c>
       <c r="R2" t="n">
-        <v>6650194.757519648</v>
+        <v>6650117</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,27 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-03-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-03-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På tallstubbe</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,29 +768,8 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -819,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132410216</v>
+        <v>132889679</v>
       </c>
       <c r="B3" t="n">
-        <v>58331</v>
+        <v>57269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -830,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100038</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -852,28 +819,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Adolfsbergsskogen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>652436</v>
+        <v>652469</v>
       </c>
       <c r="R3" t="n">
-        <v>6650254</v>
+        <v>6650249</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,22 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -942,61 +897,67 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132659867</v>
+        <v>132892109</v>
       </c>
       <c r="B4" t="n">
-        <v>56816</v>
+        <v>57269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>100038</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Columba oenas</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Wängelistorpet, Upl</t>
+          <t>Adolfsbergsskogen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>652369</v>
+        <v>652502</v>
       </c>
       <c r="R4" t="n">
-        <v>6650236</v>
+        <v>6650117</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1020,12 +981,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-07-15</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-07-15</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1052,27 +1013,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132850906</v>
+        <v>132889677</v>
       </c>
       <c r="B5" t="n">
-        <v>58641</v>
+        <v>57568</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>102963</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1087,22 +1048,27 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Roparhällarna, Upl</t>
+          <t>Adolfsbergsskogen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>652397</v>
+        <v>652469</v>
       </c>
       <c r="R5" t="n">
-        <v>6650215</v>
+        <v>6650249</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1126,22 +1092,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:11</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:11</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,39 +1112,39 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Vilhelm Amcoff</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Vilhelm Amcoff</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132893090</v>
+        <v>132892500</v>
       </c>
       <c r="B6" t="n">
-        <v>58641</v>
+        <v>57568</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103044</v>
+        <v>102963</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1201,14 +1157,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1222,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>652486</v>
+        <v>652363</v>
       </c>
       <c r="R6" t="n">
-        <v>6650197</v>
+        <v>6650308</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1284,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132893072</v>
+        <v>132892806</v>
       </c>
       <c r="B7" t="n">
-        <v>57551</v>
+        <v>57568</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1333,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>652486</v>
+        <v>652547</v>
       </c>
       <c r="R7" t="n">
-        <v>6650197</v>
+        <v>6650113</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1395,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132893083</v>
+        <v>132893072</v>
       </c>
       <c r="B8" t="n">
-        <v>58681</v>
+        <v>57568</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103055</v>
+        <v>102963</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1428,14 +1379,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1511,27 +1457,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132889683</v>
+        <v>132889698</v>
       </c>
       <c r="B9" t="n">
-        <v>58641</v>
+        <v>58519</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103044</v>
+        <v>102990</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1544,9 +1490,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1622,10 +1573,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132889677</v>
+        <v>132892114</v>
       </c>
       <c r="B10" t="n">
-        <v>57551</v>
+        <v>58519</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1633,16 +1584,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102963</v>
+        <v>102990</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1655,9 +1606,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1671,10 +1627,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>652469</v>
+        <v>652502</v>
       </c>
       <c r="R10" t="n">
-        <v>6650249</v>
+        <v>6650117</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1733,27 +1689,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132889696</v>
+        <v>132892517</v>
       </c>
       <c r="B11" t="n">
-        <v>58332</v>
+        <v>58519</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1787,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>652469</v>
+        <v>652363</v>
       </c>
       <c r="R11" t="n">
-        <v>6650249</v>
+        <v>6650308</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1849,32 +1805,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132889698</v>
+        <v>132889680</v>
       </c>
       <c r="B12" t="n">
-        <v>58502</v>
+        <v>58410</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102990</v>
+        <v>103001</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1882,14 +1838,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1965,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132893086</v>
+        <v>132892093</v>
       </c>
       <c r="B13" t="n">
-        <v>58117</v>
+        <v>58410</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1976,21 +1927,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103020</v>
+        <v>103001</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1998,14 +1949,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2019,10 +1965,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>652486</v>
+        <v>652502</v>
       </c>
       <c r="R13" t="n">
-        <v>6650197</v>
+        <v>6650117</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2081,10 +2027,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132893075</v>
+        <v>132892506</v>
       </c>
       <c r="B14" t="n">
-        <v>58090</v>
+        <v>58410</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2092,21 +2038,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205976</v>
+        <v>103001</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2130,10 +2076,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>652486</v>
+        <v>652363</v>
       </c>
       <c r="R14" t="n">
-        <v>6650197</v>
+        <v>6650308</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2192,10 +2138,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132889679</v>
+        <v>132410216</v>
       </c>
       <c r="B15" t="n">
-        <v>57252</v>
+        <v>58349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2203,21 +2149,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100038</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2225,26 +2171,28 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Adolfsbergsskogen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>652469</v>
+        <v>652436</v>
       </c>
       <c r="R15" t="n">
-        <v>6650249</v>
+        <v>6650254</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2271,12 +2219,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2303,32 +2261,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132889680</v>
+        <v>132889696</v>
       </c>
       <c r="B16" t="n">
-        <v>58393</v>
+        <v>58349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103001</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2336,9 +2294,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2414,62 +2377,67 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133159810</v>
+        <v>132892112</v>
       </c>
       <c r="B17" t="n">
-        <v>58688</v>
+        <v>58349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103055</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Roparhällarna, Upl</t>
+          <t>Adolfsbergsskogen, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>652397</v>
+        <v>652502</v>
       </c>
       <c r="R17" t="n">
-        <v>6650215</v>
+        <v>6650117</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2493,22 +2461,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:38</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:38</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2523,22 +2481,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Vilhelm Amcoff</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Vilhelm Amcoff</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133159721</v>
+        <v>132892518</v>
       </c>
       <c r="B18" t="n">
-        <v>58339</v>
+        <v>58349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2568,24 +2526,34 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Roparhällarna, Upl</t>
+          <t>Adolfsbergsskogen, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>652397</v>
+        <v>652363</v>
       </c>
       <c r="R18" t="n">
-        <v>6650215</v>
+        <v>6650308</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2609,22 +2577,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2639,44 +2597,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Vilhelm Amcoff</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Vilhelm Amcoff</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133159949</v>
+        <v>132892813</v>
       </c>
       <c r="B19" t="n">
-        <v>58126</v>
+        <v>58349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2684,24 +2642,34 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Roparhällarna, Upl</t>
+          <t>Adolfsbergsskogen, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>652397</v>
+        <v>652547</v>
       </c>
       <c r="R19" t="n">
-        <v>6650215</v>
+        <v>6650113</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2725,22 +2693,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2755,15 +2713,3386 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>133159721</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Roparhällarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>652397</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6650215</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
           <t>Vilhelm Amcoff</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
+      <c r="AX20" t="inlineStr">
         <is>
           <t>Vilhelm Amcoff</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132892516</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58134</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Adolfsbergsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>652363</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6650308</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132893086</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58134</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Adolfsbergsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>652486</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6650197</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>133159949</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Roparhällarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>652397</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6650215</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Vilhelm Amcoff</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Vilhelm Amcoff</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132889687</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Adolfsbergsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>652469</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6650249</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>132892104</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Adolfsbergsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>652502</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6650117</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>133159854</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Roparhällarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>652397</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6650215</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Vilhelm Amcoff</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Vilhelm Amcoff</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132889685</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58596</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Adolfsbergsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>652469</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6650249</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>132892102</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58596</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Adolfsbergsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>652502</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6650117</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132892513</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58596</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Adolfsbergsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>652363</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6650308</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132850969</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58624</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Roparhällarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>652496</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6650123</v>
+      </c>
+      <c r="S30" t="n">
+        <v>30</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Vilhelm Amcoff</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Vilhelm Amcoff</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>132892118</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58624</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Adolfsbergsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>652502</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6650117</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>132666098</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Roparhällarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>652496</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6650123</v>
+      </c>
+      <c r="S32" t="n">
+        <v>30</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Vilhelm Amcoff</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Vilhelm Amcoff</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>132850906</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Roparhällarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>652397</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6650215</v>
+      </c>
+      <c r="S33" t="n">
+        <v>20</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Vilhelm Amcoff</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Vilhelm Amcoff</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>132889683</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Adolfsbergsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>652469</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6650249</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>132892117</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Adolfsbergsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>652502</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6650117</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>132892522</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Adolfsbergsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>652363</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6650308</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>132892816</v>
+      </c>
+      <c r="B37" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Adolfsbergsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>652547</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6650113</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>132893090</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Adolfsbergsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>652486</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6650197</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>132892115</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58698</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Adolfsbergsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>652502</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6650117</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>132892510</v>
+      </c>
+      <c r="B40" t="n">
+        <v>58698</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Adolfsbergsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>652363</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6650308</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>132893083</v>
+      </c>
+      <c r="B41" t="n">
+        <v>58698</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Adolfsbergsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>652486</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6650197</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>133159810</v>
+      </c>
+      <c r="B42" t="n">
+        <v>58698</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Roparhällarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>652397</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6650215</v>
+      </c>
+      <c r="S42" t="n">
+        <v>20</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Vilhelm Amcoff</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Vilhelm Amcoff</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>132892807</v>
+      </c>
+      <c r="B43" t="n">
+        <v>58107</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Adolfsbergsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>652547</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6650113</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>132893075</v>
+      </c>
+      <c r="B44" t="n">
+        <v>58107</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Adolfsbergsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>652486</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6650197</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>134462233</v>
+      </c>
+      <c r="B45" t="n">
+        <v>56854</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Storvreta NO, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>652363</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6650308</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Förbiflygande några gånger</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>132659867</v>
+      </c>
+      <c r="B46" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Wängelistorpet, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>652369</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6650236</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2019-07-15</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2019-07-15</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>134462221</v>
+      </c>
+      <c r="B47" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Storvreta NO, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>652363</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6650308</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Förbiflygande många gånger</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>57751934</v>
+      </c>
+      <c r="B48" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Adolfsbergsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>652461</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6650195</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2016-03-23</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2016-03-23</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På tallstubbe</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Patrick Fritzson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
